--- a/Tracker_PowerBI_xlsx.xlsx
+++ b/Tracker_PowerBI_xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HALZABEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F57F578-93B4-4340-8A6B-4FEDC3C402F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC097CA-19A8-4F4E-BD4E-5EEB25C39181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-1425" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tracker_All" sheetId="1" r:id="rId1"/>
@@ -171,9 +171,6 @@
     <t>تأشيرة ساري سعيد تعمري القيسي</t>
   </si>
   <si>
-    <t>حالة التأشيرة: غير مستعملة</t>
-  </si>
-  <si>
     <t>GOSI Certificate</t>
   </si>
   <si>
@@ -252,9 +249,6 @@
     <t>تأشيرة مريم ايهاب محمود احمد همام</t>
   </si>
   <si>
-    <t>حالة التأشيرة: غير متوفر</t>
-  </si>
-  <si>
     <t>دليل استيراد Power BI</t>
   </si>
   <si>
@@ -304,6 +298,12 @@
   </si>
   <si>
     <t>MOSI</t>
+  </si>
+  <si>
+    <t>حالة التأشيرة: غبر مستعمل</t>
+  </si>
+  <si>
+    <t>حالة التأشيرة:  مستعمل</t>
   </si>
 </sst>
 </file>
@@ -768,7 +768,7 @@
       </c>
       <c r="F2" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="G2" s="3">
         <f>IF(E2="","",E2-30)</f>
@@ -805,7 +805,7 @@
       </c>
       <c r="F3" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G3" s="3">
         <f t="shared" ref="G3:G27" si="0">IF(E3="","",E3-30)</f>
@@ -844,7 +844,7 @@
       </c>
       <c r="F4" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G4" s="3">
         <f t="shared" si="0"/>
@@ -883,7 +883,7 @@
       </c>
       <c r="F5" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G5" s="3">
         <f t="shared" si="0"/>
@@ -922,7 +922,7 @@
       </c>
       <c r="F6" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G6" s="3">
         <f t="shared" si="0"/>
@@ -961,7 +961,7 @@
       </c>
       <c r="F7" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="G7" s="3">
         <f t="shared" si="0"/>
@@ -994,29 +994,29 @@
         <v>32</v>
       </c>
       <c r="E8" s="6">
-        <v>46172</v>
+        <v>46216</v>
       </c>
       <c r="F8" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="0"/>
-        <v>46142</v>
+        <v>46186</v>
       </c>
       <c r="H8" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>حرج</v>
+        <v>ساري</v>
       </c>
       <c r="I8" s="7" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>عالية</v>
+        <v>منخفضة</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>33</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="F9" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G9" s="3">
         <f t="shared" si="0"/>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F10" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G10" s="3">
         <f t="shared" si="0"/>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="F11" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G11" s="3">
         <f t="shared" si="0"/>
@@ -1123,11 +1123,11 @@
       </c>
       <c r="H11" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>قريب</v>
+        <v>حرج</v>
       </c>
       <c r="I11" s="7" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>متوسطة</v>
+        <v>عالية</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>33</v>
@@ -1150,29 +1150,29 @@
         <v>44</v>
       </c>
       <c r="E12" s="8">
-        <v>46204</v>
+        <v>46232</v>
       </c>
       <c r="F12" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="G12" s="3">
         <f t="shared" si="0"/>
-        <v>46174</v>
+        <v>46202</v>
       </c>
       <c r="H12" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>قريب</v>
+        <v>ساري</v>
       </c>
       <c r="I12" s="7" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>متوسطة</v>
+        <v>منخفضة</v>
       </c>
       <c r="J12" s="7" t="s">
         <v>33</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
@@ -1180,20 +1180,20 @@
         <v>11</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>47</v>
-      </c>
       <c r="D13" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E13" s="8">
         <v>46213</v>
       </c>
       <c r="F13" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G13" s="3">
         <f t="shared" si="0"/>
@@ -1201,11 +1201,11 @@
       </c>
       <c r="H13" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ساري</v>
+        <v>قريب</v>
       </c>
       <c r="I13" s="7" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>منخفضة</v>
+        <v>متوسطة</v>
       </c>
       <c r="J13" s="7" t="s">
         <v>14</v>
@@ -1220,21 +1220,21 @@
         <v>30</v>
       </c>
       <c r="C14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>49</v>
-      </c>
       <c r="E14" s="8">
-        <v>46214</v>
+        <v>46469</v>
       </c>
       <c r="F14" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>65</v>
+        <v>316</v>
       </c>
       <c r="G14" s="3">
         <f t="shared" si="0"/>
-        <v>46184</v>
+        <v>46439</v>
       </c>
       <c r="H14" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -1248,7 +1248,7 @@
         <v>33</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
@@ -1256,20 +1256,20 @@
         <v>11</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="D15" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>52</v>
       </c>
       <c r="E15" s="8">
         <v>46235</v>
       </c>
       <c r="F15" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G15" s="3">
         <f t="shared" si="0"/>
@@ -1299,14 +1299,14 @@
         <v>43</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E16" s="8">
         <v>46344</v>
       </c>
       <c r="F16" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="G16" s="3">
         <f t="shared" si="0"/>
@@ -1324,7 +1324,7 @@
         <v>33</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -1338,14 +1338,14 @@
         <v>21</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E17" s="8">
         <v>46391</v>
       </c>
       <c r="F17" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="G17" s="3">
         <f t="shared" si="0"/>
@@ -1377,14 +1377,14 @@
         <v>24</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E18" s="8">
         <v>46391</v>
       </c>
       <c r="F18" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="G18" s="3">
         <f t="shared" si="0"/>
@@ -1410,20 +1410,20 @@
         <v>11</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="D19" s="7" t="s">
         <v>58</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>59</v>
       </c>
       <c r="E19" s="8">
         <v>46396</v>
       </c>
       <c r="F19" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G19" s="3">
         <f t="shared" si="0"/>
@@ -1455,14 +1455,14 @@
         <v>31</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E20" s="8">
         <v>46527</v>
       </c>
       <c r="F20" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="G20" s="3">
         <f t="shared" si="0"/>
@@ -1480,7 +1480,7 @@
         <v>33</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
@@ -1494,14 +1494,14 @@
         <v>41</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E21" s="8">
         <v>46535</v>
       </c>
       <c r="F21" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="G21" s="3">
         <f t="shared" si="0"/>
@@ -1519,7 +1519,7 @@
         <v>33</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
@@ -1530,17 +1530,17 @@
         <v>35</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E22" s="8">
         <v>46554</v>
       </c>
       <c r="F22" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="G22" s="3">
         <f t="shared" si="0"/>
@@ -1558,7 +1558,7 @@
         <v>33</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
@@ -1566,13 +1566,13 @@
         <v>11</v>
       </c>
       <c r="B23" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="9" t="s">
-        <v>51</v>
-      </c>
       <c r="D23" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E23" s="9"/>
       <c r="F23" s="10"/>
@@ -1598,13 +1598,13 @@
         <v>11</v>
       </c>
       <c r="B24" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="D24" s="9" t="s">
         <v>68</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>69</v>
       </c>
       <c r="E24" s="9"/>
       <c r="F24" s="10"/>
@@ -1624,7 +1624,7 @@
         <v>14</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
@@ -1638,27 +1638,32 @@
         <v>36</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E25" s="9"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <v>70</v>
+      </c>
+      <c r="E25" s="8">
+        <v>46215</v>
+      </c>
+      <c r="F25" s="4">
+        <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
+        <v>62</v>
+      </c>
+      <c r="G25" s="3">
+        <f t="shared" si="0"/>
+        <v>46185</v>
       </c>
       <c r="H25" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>بدون تاريخ</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>ساري</v>
       </c>
       <c r="I25" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>مراجعة مطلوبة</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>منخفضة</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>33</v>
       </c>
       <c r="K25" s="9" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
@@ -1666,13 +1671,13 @@
         <v>11</v>
       </c>
       <c r="B26" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="D26" s="9" t="s">
         <v>68</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>69</v>
       </c>
       <c r="E26" s="9"/>
       <c r="F26" s="10"/>
@@ -1692,7 +1697,7 @@
         <v>14</v>
       </c>
       <c r="K26" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
@@ -1700,20 +1705,20 @@
         <v>11</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E27" s="8">
         <v>46398</v>
       </c>
       <c r="F27" s="4">
         <f ca="1">E27-TODAY()</f>
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="G27" s="3">
         <f t="shared" si="0"/>
@@ -1758,7 +1763,7 @@
     <row r="2" spans="1:2" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11"/>
       <c r="B2" s="13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -1767,42 +1772,42 @@
     </row>
     <row r="4" spans="1:2" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -1812,7 +1817,7 @@
     <row r="10" spans="1:2" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11"/>
       <c r="B10" s="14" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -1822,7 +1827,7 @@
     <row r="12" spans="1:2" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -1832,7 +1837,7 @@
     <row r="14" spans="1:2" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11"/>
       <c r="B14" s="14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -1842,7 +1847,7 @@
     <row r="16" spans="1:2" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11"/>
       <c r="B16" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/Tracker_PowerBI_xlsx.xlsx
+++ b/Tracker_PowerBI_xlsx.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HALZABEN\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://meirc-my.sharepoint.com/personal/halzaben_meirc_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC097CA-19A8-4F4E-BD4E-5EEB25C39181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{AFC097CA-19A8-4F4E-BD4E-5EEB25C39181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A174FA2-0D83-4863-94E2-466FB797B6A0}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1425" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tracker_All" sheetId="1" r:id="rId1"/>
@@ -300,10 +300,10 @@
     <t>MOSI</t>
   </si>
   <si>
-    <t>حالة التأشيرة: غبر مستعمل</t>
-  </si>
-  <si>
     <t>حالة التأشيرة:  مستعمل</t>
+  </si>
+  <si>
+    <t>حالة التأشيرة: غبر مستعمل - السفر قبل</t>
   </si>
 </sst>
 </file>
@@ -768,7 +768,7 @@
       </c>
       <c r="F2" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G2" s="3">
         <f>IF(E2="","",E2-30)</f>
@@ -805,7 +805,7 @@
       </c>
       <c r="F3" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G3" s="3">
         <f t="shared" ref="G3:G27" si="0">IF(E3="","",E3-30)</f>
@@ -844,7 +844,7 @@
       </c>
       <c r="F4" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G4" s="3">
         <f t="shared" si="0"/>
@@ -883,7 +883,7 @@
       </c>
       <c r="F5" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G5" s="3">
         <f t="shared" si="0"/>
@@ -922,7 +922,7 @@
       </c>
       <c r="F6" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G6" s="3">
         <f t="shared" si="0"/>
@@ -961,7 +961,7 @@
       </c>
       <c r="F7" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="G7" s="3">
         <f t="shared" si="0"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="F8" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="0"/>
@@ -1016,7 +1016,7 @@
         <v>33</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="F9" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G9" s="3">
         <f t="shared" si="0"/>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F10" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G10" s="3">
         <f t="shared" si="0"/>
@@ -1111,29 +1111,29 @@
         <v>42</v>
       </c>
       <c r="E11" s="6">
-        <v>46182</v>
+        <v>46245</v>
       </c>
       <c r="F11" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="G11" s="3">
         <f t="shared" si="0"/>
-        <v>46152</v>
+        <v>46215</v>
       </c>
       <c r="H11" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>حرج</v>
+        <v>ساري</v>
       </c>
       <c r="I11" s="7" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>عالية</v>
+        <v>منخفضة</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>33</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="F12" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G12" s="3">
         <f t="shared" si="0"/>
@@ -1172,7 +1172,7 @@
         <v>33</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F13" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G13" s="3">
         <f t="shared" si="0"/>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="F14" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G14" s="3">
         <f t="shared" si="0"/>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="F15" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G15" s="3">
         <f t="shared" si="0"/>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="F16" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G16" s="3">
         <f t="shared" si="0"/>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="F17" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G17" s="3">
         <f t="shared" si="0"/>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="F18" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G18" s="3">
         <f t="shared" si="0"/>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F19" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G19" s="3">
         <f t="shared" si="0"/>
@@ -1458,7 +1458,7 @@
         <v>59</v>
       </c>
       <c r="E20" s="8">
-        <v>46527</v>
+        <v>46529</v>
       </c>
       <c r="F20" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="G20" s="3">
         <f t="shared" si="0"/>
-        <v>46497</v>
+        <v>46499</v>
       </c>
       <c r="H20" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="F21" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G21" s="3">
         <f t="shared" si="0"/>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="F22" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G22" s="3">
         <f t="shared" si="0"/>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F25" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G25" s="3">
         <f t="shared" si="0"/>
@@ -1653,17 +1653,17 @@
       </c>
       <c r="H25" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ساري</v>
+        <v>قريب</v>
       </c>
       <c r="I25" s="7" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>منخفضة</v>
+        <v>متوسطة</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>33</v>
       </c>
       <c r="K25" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="F27" s="4">
         <f ca="1">E27-TODAY()</f>
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G27" s="3">
         <f t="shared" si="0"/>

--- a/Tracker_PowerBI_xlsx.xlsx
+++ b/Tracker_PowerBI_xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://meirc-my.sharepoint.com/personal/halzaben_meirc_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{AFC097CA-19A8-4F4E-BD4E-5EEB25C39181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A174FA2-0D83-4863-94E2-466FB797B6A0}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{AFC097CA-19A8-4F4E-BD4E-5EEB25C39181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8EB5F6E-90A0-4A81-8384-0B8F76FEFF9C}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-1425" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tracker_All" sheetId="1" r:id="rId1"/>
@@ -496,6 +496,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -768,7 +772,7 @@
       </c>
       <c r="F2" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="G2" s="3">
         <f>IF(E2="","",E2-30)</f>
@@ -805,7 +809,7 @@
       </c>
       <c r="F3" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G3" s="3">
         <f t="shared" ref="G3:G27" si="0">IF(E3="","",E3-30)</f>
@@ -844,7 +848,7 @@
       </c>
       <c r="F4" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G4" s="3">
         <f t="shared" si="0"/>
@@ -879,23 +883,23 @@
         <v>22</v>
       </c>
       <c r="E5" s="3">
-        <v>46167</v>
+        <v>46532</v>
       </c>
       <c r="F5" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>12</v>
+        <v>373</v>
       </c>
       <c r="G5" s="3">
         <f t="shared" si="0"/>
-        <v>46137</v>
+        <v>46502</v>
       </c>
       <c r="H5" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>حرج</v>
+        <v>ساري</v>
       </c>
       <c r="I5" s="7" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>عالية</v>
+        <v>منخفضة</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>14</v>
@@ -918,23 +922,23 @@
         <v>25</v>
       </c>
       <c r="E6" s="3">
-        <v>46167</v>
+        <v>46532</v>
       </c>
       <c r="F6" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>12</v>
+        <v>373</v>
       </c>
       <c r="G6" s="3">
         <f t="shared" si="0"/>
-        <v>46137</v>
+        <v>46502</v>
       </c>
       <c r="H6" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>حرج</v>
+        <v>ساري</v>
       </c>
       <c r="I6" s="7" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>عالية</v>
+        <v>منخفضة</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>14</v>
@@ -961,7 +965,7 @@
       </c>
       <c r="F7" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="G7" s="3">
         <f t="shared" si="0"/>
@@ -998,7 +1002,7 @@
       </c>
       <c r="F8" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="0"/>
@@ -1006,11 +1010,11 @@
       </c>
       <c r="H8" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ساري</v>
+        <v>قريب</v>
       </c>
       <c r="I8" s="7" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>منخفضة</v>
+        <v>متوسطة</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>33</v>
@@ -1037,7 +1041,7 @@
       </c>
       <c r="F9" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G9" s="3">
         <f t="shared" si="0"/>
@@ -1076,7 +1080,7 @@
       </c>
       <c r="F10" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G10" s="3">
         <f t="shared" si="0"/>
@@ -1115,7 +1119,7 @@
       </c>
       <c r="F11" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G11" s="3">
         <f t="shared" si="0"/>
@@ -1154,7 +1158,7 @@
       </c>
       <c r="F12" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G12" s="3">
         <f t="shared" si="0"/>
@@ -1193,7 +1197,7 @@
       </c>
       <c r="F13" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G13" s="3">
         <f t="shared" si="0"/>
@@ -1230,7 +1234,7 @@
       </c>
       <c r="F14" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="G14" s="3">
         <f t="shared" si="0"/>
@@ -1269,7 +1273,7 @@
       </c>
       <c r="F15" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G15" s="3">
         <f t="shared" si="0"/>
@@ -1306,7 +1310,7 @@
       </c>
       <c r="F16" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G16" s="3">
         <f t="shared" si="0"/>
@@ -1345,7 +1349,7 @@
       </c>
       <c r="F17" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G17" s="3">
         <f t="shared" si="0"/>
@@ -1384,7 +1388,7 @@
       </c>
       <c r="F18" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G18" s="3">
         <f t="shared" si="0"/>
@@ -1423,7 +1427,7 @@
       </c>
       <c r="F19" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="G19" s="3">
         <f t="shared" si="0"/>
@@ -1462,7 +1466,7 @@
       </c>
       <c r="F20" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="G20" s="3">
         <f t="shared" si="0"/>
@@ -1501,7 +1505,7 @@
       </c>
       <c r="F21" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="G21" s="3">
         <f t="shared" si="0"/>
@@ -1540,7 +1544,7 @@
       </c>
       <c r="F22" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="G22" s="3">
         <f t="shared" si="0"/>
@@ -1645,7 +1649,7 @@
       </c>
       <c r="F25" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G25" s="3">
         <f t="shared" si="0"/>
@@ -1718,7 +1722,7 @@
       </c>
       <c r="F27" s="4">
         <f ca="1">E27-TODAY()</f>
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G27" s="3">
         <f t="shared" si="0"/>

--- a/Tracker_PowerBI_xlsx.xlsx
+++ b/Tracker_PowerBI_xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://meirc-my.sharepoint.com/personal/halzaben_meirc_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{AFC097CA-19A8-4F4E-BD4E-5EEB25C39181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8EB5F6E-90A0-4A81-8384-0B8F76FEFF9C}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{AFC097CA-19A8-4F4E-BD4E-5EEB25C39181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FA77272-8934-49BE-AAEA-F048A1A785CC}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1425" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tracker_All" sheetId="1" r:id="rId1"/>
@@ -1037,23 +1037,23 @@
         <v>37</v>
       </c>
       <c r="E9" s="6">
-        <v>46175</v>
+        <v>46529</v>
       </c>
       <c r="F9" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>16</v>
+        <v>370</v>
       </c>
       <c r="G9" s="3">
         <f t="shared" si="0"/>
-        <v>46145</v>
+        <v>46499</v>
       </c>
       <c r="H9" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>حرج</v>
+        <v>ساري</v>
       </c>
       <c r="I9" s="7" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>عالية</v>
+        <v>منخفضة</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>33</v>

--- a/Tracker_PowerBI_xlsx.xlsx
+++ b/Tracker_PowerBI_xlsx.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://meirc-my.sharepoint.com/personal/halzaben_meirc_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{AFC097CA-19A8-4F4E-BD4E-5EEB25C39181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FA77272-8934-49BE-AAEA-F048A1A785CC}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{AFC097CA-19A8-4F4E-BD4E-5EEB25C39181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64123EF2-D323-4511-A58E-005D24FB0A3D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-1425" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tracker_All" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="92">
   <si>
     <t>المصدر</t>
   </si>
@@ -304,6 +304,12 @@
   </si>
   <si>
     <t>حالة التأشيرة: غبر مستعمل - السفر قبل</t>
+  </si>
+  <si>
+    <t>Monshaat 42</t>
+  </si>
+  <si>
+    <t>Monshaat 32</t>
   </si>
 </sst>
 </file>
@@ -359,7 +365,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -384,6 +390,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF1EFE8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
   </fills>
@@ -414,7 +426,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -456,6 +468,9 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -703,7 +718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -772,7 +787,7 @@
       </c>
       <c r="F2" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="G2" s="3">
         <f>IF(E2="","",E2-30)</f>
@@ -809,7 +824,7 @@
       </c>
       <c r="F3" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="G3" s="3">
         <f t="shared" ref="G3:G27" si="0">IF(E3="","",E3-30)</f>
@@ -848,7 +863,7 @@
       </c>
       <c r="F4" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="G4" s="3">
         <f t="shared" si="0"/>
@@ -856,11 +871,11 @@
       </c>
       <c r="H4" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ساري</v>
+        <v>قريب</v>
       </c>
       <c r="I4" s="7" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>منخفضة</v>
+        <v>متوسطة</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>14</v>
@@ -887,7 +902,7 @@
       </c>
       <c r="F5" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="G5" s="3">
         <f t="shared" si="0"/>
@@ -926,7 +941,7 @@
       </c>
       <c r="F6" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="G6" s="3">
         <f t="shared" si="0"/>
@@ -965,7 +980,7 @@
       </c>
       <c r="F7" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>792</v>
+        <v>776</v>
       </c>
       <c r="G7" s="3">
         <f t="shared" si="0"/>
@@ -1002,7 +1017,7 @@
       </c>
       <c r="F8" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="0"/>
@@ -1041,7 +1056,7 @@
       </c>
       <c r="F9" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>370</v>
+        <v>354</v>
       </c>
       <c r="G9" s="3">
         <f t="shared" si="0"/>
@@ -1073,26 +1088,26 @@
         <v>40</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="E10" s="6">
-        <v>46176</v>
+        <v>46526</v>
       </c>
       <c r="F10" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>17</v>
+        <v>351</v>
       </c>
       <c r="G10" s="3">
         <f t="shared" si="0"/>
-        <v>46146</v>
+        <v>46496</v>
       </c>
       <c r="H10" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>حرج</v>
+        <v>ساري</v>
       </c>
       <c r="I10" s="7" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>عالية</v>
+        <v>منخفضة</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>14</v>
@@ -1119,7 +1134,7 @@
       </c>
       <c r="F11" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="G11" s="3">
         <f t="shared" si="0"/>
@@ -1158,7 +1173,7 @@
       </c>
       <c r="F12" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="G12" s="3">
         <f t="shared" si="0"/>
@@ -1166,11 +1181,11 @@
       </c>
       <c r="H12" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ساري</v>
+        <v>قريب</v>
       </c>
       <c r="I12" s="7" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>منخفضة</v>
+        <v>متوسطة</v>
       </c>
       <c r="J12" s="7" t="s">
         <v>33</v>
@@ -1197,7 +1212,7 @@
       </c>
       <c r="F13" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="G13" s="3">
         <f t="shared" si="0"/>
@@ -1234,7 +1249,7 @@
       </c>
       <c r="F14" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="G14" s="3">
         <f t="shared" si="0"/>
@@ -1273,7 +1288,7 @@
       </c>
       <c r="F15" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="G15" s="3">
         <f t="shared" si="0"/>
@@ -1281,11 +1296,11 @@
       </c>
       <c r="H15" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ساري</v>
+        <v>قريب</v>
       </c>
       <c r="I15" s="7" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>منخفضة</v>
+        <v>متوسطة</v>
       </c>
       <c r="J15" s="7" t="s">
         <v>14</v>
@@ -1310,7 +1325,7 @@
       </c>
       <c r="F16" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="G16" s="3">
         <f t="shared" si="0"/>
@@ -1349,7 +1364,7 @@
       </c>
       <c r="F17" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="G17" s="3">
         <f t="shared" si="0"/>
@@ -1388,7 +1403,7 @@
       </c>
       <c r="F18" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="G18" s="3">
         <f t="shared" si="0"/>
@@ -1427,7 +1442,7 @@
       </c>
       <c r="F19" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="G19" s="3">
         <f t="shared" si="0"/>
@@ -1466,7 +1481,7 @@
       </c>
       <c r="F20" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>370</v>
+        <v>354</v>
       </c>
       <c r="G20" s="3">
         <f t="shared" si="0"/>
@@ -1505,7 +1520,7 @@
       </c>
       <c r="F21" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="G21" s="3">
         <f t="shared" si="0"/>
@@ -1544,7 +1559,7 @@
       </c>
       <c r="F22" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="G22" s="3">
         <f t="shared" si="0"/>
@@ -1649,7 +1664,7 @@
       </c>
       <c r="F25" s="4">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="G25" s="3">
         <f t="shared" si="0"/>
@@ -1722,7 +1737,7 @@
       </c>
       <c r="F27" s="4">
         <f ca="1">E27-TODAY()</f>
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="G27" s="3">
         <f t="shared" si="0"/>
@@ -1740,6 +1755,45 @@
         <v>14</v>
       </c>
       <c r="K27" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E28" s="6">
+        <v>46526</v>
+      </c>
+      <c r="F28" s="4">
+        <f ca="1">E28-TODAY()</f>
+        <v>351</v>
+      </c>
+      <c r="G28" s="3">
+        <f t="shared" ref="G28" si="6">IF(E28="","",E28-30)</f>
+        <v>46496</v>
+      </c>
+      <c r="H28" s="15" t="str">
+        <f t="shared" ref="H28" ca="1" si="7">IF(E28="","بدون تاريخ",IF(F28&lt;0,"منتهي",IF(F28&lt;=30,"حرج",IF(F28&lt;=60,"قريب","ساري"))))</f>
+        <v>ساري</v>
+      </c>
+      <c r="I28" s="15" t="str">
+        <f t="shared" ref="I28" ca="1" si="8">IF(H28="بدون تاريخ","مراجعة مطلوبة",IF(H28="منتهي","عالية",IF(H28="حرج","عالية",IF(H28="قريب","متوسطة","منخفضة"))))</f>
+        <v>منخفضة</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K28" s="5" t="s">
         <v>18</v>
       </c>
     </row>

--- a/Tracker_PowerBI_xlsx.xlsx
+++ b/Tracker_PowerBI_xlsx.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HALZABEN\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://meirc-my.sharepoint.com/personal/halzaben_meirc_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9DB5D68-FAF6-475D-815D-D63DA13F66D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{A9DB5D68-FAF6-475D-815D-D63DA13F66D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1443B46E-11AE-41CF-BEE9-4BE57C6147F1}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1425" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tracker_All" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="164">
   <si>
     <t>المصدر</t>
   </si>
@@ -1100,18 +1100,6 @@
   </si>
   <si>
     <t>National address 32</t>
-  </si>
-  <si>
-    <t>VAT Certificate</t>
-  </si>
-  <si>
-    <t>ZATCA / VAT</t>
-  </si>
-  <si>
-    <t>VAT</t>
-  </si>
-  <si>
-    <t>Uploaded doc is Tax Residency Cert.</t>
   </si>
   <si>
     <t>تأشيرة مريم ايهاب محمود احمد همام</t>
@@ -1406,7 +1394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1436,9 +1424,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -1541,7 +1526,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tracker_All" displayName="Tracker_All" ref="A1:K20" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tracker_All" displayName="Tracker_All" ref="A1:K18" totalsRowShown="0">
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="المصدر"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="النوع"/>
@@ -1702,7 +1687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R24"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1796,15 +1781,15 @@
         <v>250</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G24" si="0">IF(E2="","",E2-30)</f>
+        <f t="shared" ref="G2:G21" si="0">IF(E2="","",E2-30)</f>
         <v>46477</v>
       </c>
       <c r="H2" s="6" t="str">
-        <f t="shared" ref="H2:H24" ca="1" si="1">IF(E2="","بدون تاريخ",IF(F2&lt;0,"منتهي",IF(F2&lt;=30,"حرج",IF(F2&lt;=60,"قريب","ساري"))))</f>
+        <f t="shared" ref="H2:H21" ca="1" si="1">IF(E2="","بدون تاريخ",IF(F2&lt;0,"منتهي",IF(F2&lt;=30,"حرج",IF(F2&lt;=60,"قريب","ساري"))))</f>
         <v>ساري</v>
       </c>
       <c r="I2" s="6" t="str">
-        <f t="shared" ref="I2:I24" ca="1" si="2">IF(H2="بدون تاريخ","مراجعة مطلوبة",IF(H2="منتهي","عالية",IF(H2="حرج","عالية",IF(H2="قريب","متوسطة","منخفضة"))))</f>
+        <f t="shared" ref="I2:I21" ca="1" si="2">IF(H2="بدون تاريخ","مراجعة مطلوبة",IF(H2="منتهي","عالية",IF(H2="حرج","عالية",IF(H2="قريب","متوسطة","منخفضة"))))</f>
         <v>منخفضة</v>
       </c>
       <c r="J2" s="3" t="s">
@@ -1938,7 +1923,7 @@
         <v>34</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="O4" t="s">
         <v>40</v>
@@ -2238,7 +2223,7 @@
         <v>90</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E10" s="10">
         <v>46284</v>
@@ -2699,255 +2684,155 @@
       </c>
     </row>
     <row r="19" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="E19" s="11"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="4" t="str">
+      <c r="B19" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="E19" s="10">
+        <v>46398</v>
+      </c>
+      <c r="F19" s="5">
+        <f ca="1">E19-TODAY()</f>
+        <v>141</v>
+      </c>
+      <c r="G19" s="4">
+        <f t="shared" si="0"/>
+        <v>46368</v>
+      </c>
+      <c r="H19" s="6" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>ساري</v>
+      </c>
+      <c r="I19" s="6" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>منخفضة</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="14.25" customHeight="1">
+      <c r="A20" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E20" s="9">
+        <v>46526</v>
+      </c>
+      <c r="F20" s="5">
+        <f ca="1">E20-TODAY()</f>
+        <v>269</v>
+      </c>
+      <c r="G20" s="4">
+        <f t="shared" si="0"/>
+        <v>46496</v>
+      </c>
+      <c r="H20" s="12" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>ساري</v>
+      </c>
+      <c r="I20" s="12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>منخفضة</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="O20" t="s">
+        <v>84</v>
+      </c>
+      <c r="P20" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>27</v>
+      </c>
+      <c r="R20" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
+      <c r="A21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>140</v>
+      </c>
+      <c r="C21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" t="s">
+        <v>141</v>
+      </c>
+      <c r="G21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H19" s="6" t="str">
+      <c r="H21" t="str">
         <f t="shared" si="1"/>
         <v>بدون تاريخ</v>
       </c>
-      <c r="I19" s="6" t="str">
+      <c r="I21" t="str">
         <f t="shared" si="2"/>
         <v>مراجعة مطلوبة</v>
       </c>
-      <c r="J19" s="11" t="s">
+      <c r="J21" t="s">
         <v>21</v>
       </c>
-      <c r="K19" s="11"/>
-    </row>
-    <row r="20" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A20" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="E20" s="11"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H20" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>بدون تاريخ</v>
-      </c>
-      <c r="I20" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>مراجعة مطلوبة</v>
-      </c>
-      <c r="J20" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K20" s="11" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A21" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="E21" s="11"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H21" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>بدون تاريخ</v>
-      </c>
-      <c r="I21" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>مراجعة مطلوبة</v>
-      </c>
-      <c r="J21" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K21" s="11" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A22" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="E22" s="10">
-        <v>46398</v>
-      </c>
-      <c r="F22" s="5">
-        <f ca="1">E22-TODAY()</f>
-        <v>141</v>
-      </c>
-      <c r="G22" s="4">
-        <f t="shared" si="0"/>
-        <v>46368</v>
-      </c>
-      <c r="H22" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ساري</v>
-      </c>
-      <c r="I22" s="6" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>منخفضة</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="K22" s="6" t="s">
+      <c r="K21" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="23" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A23" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="E23" s="9">
-        <v>46526</v>
-      </c>
-      <c r="F23" s="5">
-        <f ca="1">E23-TODAY()</f>
-        <v>269</v>
-      </c>
-      <c r="G23" s="4">
-        <f t="shared" si="0"/>
-        <v>46496</v>
-      </c>
-      <c r="H23" s="13" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ساري</v>
-      </c>
-      <c r="I23" s="13" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>منخفضة</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="K23" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="L23" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="M23" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="N23" s="7" t="s">
+      <c r="L21" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="O23" t="s">
-        <v>84</v>
-      </c>
-      <c r="P23" t="s">
+      <c r="M21" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N21" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="O21" t="s">
+        <v>144</v>
+      </c>
+      <c r="P21" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q21" t="s">
         <v>27</v>
       </c>
-      <c r="R23" s="7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18">
-      <c r="A24" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" t="s">
-        <v>144</v>
-      </c>
-      <c r="C24" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" t="s">
-        <v>145</v>
-      </c>
-      <c r="G24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H24" t="str">
-        <f t="shared" si="1"/>
-        <v>بدون تاريخ</v>
-      </c>
-      <c r="I24" t="str">
-        <f t="shared" si="2"/>
-        <v>مراجعة مطلوبة</v>
-      </c>
-      <c r="J24" t="s">
-        <v>21</v>
-      </c>
-      <c r="K24" t="s">
-        <v>32</v>
-      </c>
-      <c r="L24" s="7" t="s">
+      <c r="R21" t="s">
         <v>146</v>
-      </c>
-      <c r="M24" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N24" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="O24" t="s">
-        <v>148</v>
-      </c>
-      <c r="P24" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>27</v>
-      </c>
-      <c r="R24" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -2969,97 +2854,97 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A1" s="14"/>
-      <c r="B1" s="15"/>
+      <c r="A1" s="13"/>
+      <c r="B1" s="14"/>
     </row>
     <row r="2" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A2" s="14"/>
-      <c r="B2" s="16" t="s">
+      <c r="A2" s="13"/>
+      <c r="B2" s="15" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A3" s="13"/>
+      <c r="B3" s="14"/>
+    </row>
+    <row r="4" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A4" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A5" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A3" s="14"/>
-      <c r="B3" s="15"/>
-    </row>
-    <row r="4" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A4" s="14" t="s">
+    <row r="6" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A6" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B6" s="14" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A5" s="14" t="s">
+    <row r="7" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A7" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B7" s="14" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A6" s="14" t="s">
+    <row r="8" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A8" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B8" s="14" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A7" s="14" t="s">
+    <row r="9" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A9" s="13"/>
+      <c r="B9" s="14"/>
+    </row>
+    <row r="10" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A10" s="13"/>
+      <c r="B10" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="B7" s="15" t="s">
+    </row>
+    <row r="11" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A11" s="13"/>
+      <c r="B11" s="14"/>
+    </row>
+    <row r="12" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A12" s="13"/>
+      <c r="B12" s="16" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A8" s="14" t="s">
+    <row r="13" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A13" s="13"/>
+      <c r="B13" s="14"/>
+    </row>
+    <row r="14" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A14" s="13"/>
+      <c r="B14" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="B8" s="15" t="s">
+    </row>
+    <row r="15" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A15" s="13"/>
+      <c r="B15" s="14"/>
+    </row>
+    <row r="16" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A16" s="13"/>
+      <c r="B16" s="16" t="s">
         <v>161</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A9" s="14"/>
-      <c r="B9" s="15"/>
-    </row>
-    <row r="10" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A10" s="14"/>
-      <c r="B10" s="17" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A11" s="14"/>
-      <c r="B11" s="15"/>
-    </row>
-    <row r="12" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A12" s="14"/>
-      <c r="B12" s="17" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A13" s="14"/>
-      <c r="B13" s="15"/>
-    </row>
-    <row r="14" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A14" s="14"/>
-      <c r="B14" s="17" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A15" s="14"/>
-      <c r="B15" s="15"/>
-    </row>
-    <row r="16" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A16" s="14"/>
-      <c r="B16" s="17" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="14.25" customHeight="1">
@@ -3078,21 +2963,21 @@
       <c r="E19" s="9">
         <v>46529</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="5" t="e">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>-46257</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G19" s="4">
         <f>IF(E19="","",E19-30)</f>
         <v>46499</v>
       </c>
-      <c r="H19" s="6" t="str">
+      <c r="H19" s="6" t="e">
         <f ca="1">IF(E19="","بدون تاريخ",IF(F19&lt;0,"منتهي",IF(F19&lt;=30,"حرج",IF(F19&lt;=60,"قريب","ساري"))))</f>
-        <v>منتهي</v>
-      </c>
-      <c r="I19" s="6" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I19" s="6" t="e">
         <f ca="1">IF(H19="بدون تاريخ","مراجعة مطلوبة",IF(H19="منتهي","عالية",IF(H19="حرج","عالية",IF(H19="قريب","متوسطة","منخفضة"))))</f>
-        <v>عالية</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J19" s="8" t="s">
         <v>72</v>
@@ -3112,26 +2997,26 @@
         <v>75</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E20" s="10">
         <v>46215</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="5" t="e">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>-46257</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G20" s="4">
         <f>IF(E20="","",E20-30)</f>
         <v>46185</v>
       </c>
-      <c r="H20" s="6" t="str">
+      <c r="H20" s="6" t="e">
         <f ca="1">IF(E20="","بدون تاريخ",IF(F20&lt;0,"منتهي",IF(F20&lt;=30,"حرج",IF(F20&lt;=60,"قريب","ساري"))))</f>
-        <v>منتهي</v>
-      </c>
-      <c r="I20" s="6" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I20" s="6" t="e">
         <f ca="1">IF(H20="بدون تاريخ","مراجعة مطلوبة",IF(H20="منتهي","عالية",IF(H20="حرج","عالية",IF(H20="قريب","متوسطة","منخفضة"))))</f>
-        <v>عالية</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J20" s="11" t="s">
         <v>72</v>

--- a/Tracker_PowerBI_xlsx.xlsx
+++ b/Tracker_PowerBI_xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://meirc-my.sharepoint.com/personal/halzaben_meirc_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{A9DB5D68-FAF6-475D-815D-D63DA13F66D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1443B46E-11AE-41CF-BEE9-4BE57C6147F1}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{A9DB5D68-FAF6-475D-815D-D63DA13F66D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2A48B39-E1C0-44A5-9812-E3D0BFEBD3C2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="157">
   <si>
     <t>المصدر</t>
   </si>
@@ -1135,70 +1135,6 @@
   </si>
   <si>
     <t>SME - CR32.pdf</t>
-  </si>
-  <si>
-    <t>Tax Residency Certificate</t>
-  </si>
-  <si>
-    <t>Tax Residency – CR32</t>
-  </si>
-  <si>
-    <t>شهادة الإقامة الضريبية</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>رقم الشهادة</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 100261168150256</t>
-    </r>
-  </si>
-  <si>
-    <t>07/04/2026</t>
-  </si>
-  <si>
-    <t>Tax-Residency-ZATCA.pdf</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CR: 1010813032 · TIN: 3116554691 · </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">صالح لعام </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>2026</t>
-    </r>
   </si>
   <si>
     <t>دليل استيراد Power BI</t>
@@ -1687,7 +1623,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1781,15 +1717,15 @@
         <v>250</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G21" si="0">IF(E2="","",E2-30)</f>
+        <f t="shared" ref="G2:G20" si="0">IF(E2="","",E2-30)</f>
         <v>46477</v>
       </c>
       <c r="H2" s="6" t="str">
-        <f t="shared" ref="H2:H21" ca="1" si="1">IF(E2="","بدون تاريخ",IF(F2&lt;0,"منتهي",IF(F2&lt;=30,"حرج",IF(F2&lt;=60,"قريب","ساري"))))</f>
+        <f t="shared" ref="H2:H20" ca="1" si="1">IF(E2="","بدون تاريخ",IF(F2&lt;0,"منتهي",IF(F2&lt;=30,"حرج",IF(F2&lt;=60,"قريب","ساري"))))</f>
         <v>ساري</v>
       </c>
       <c r="I2" s="6" t="str">
-        <f t="shared" ref="I2:I21" ca="1" si="2">IF(H2="بدون تاريخ","مراجعة مطلوبة",IF(H2="منتهي","عالية",IF(H2="حرج","عالية",IF(H2="قريب","متوسطة","منخفضة"))))</f>
+        <f t="shared" ref="I2:I20" ca="1" si="2">IF(H2="بدون تاريخ","مراجعة مطلوبة",IF(H2="منتهي","عالية",IF(H2="حرج","عالية",IF(H2="قريب","متوسطة","منخفضة"))))</f>
         <v>منخفضة</v>
       </c>
       <c r="J2" s="3" t="s">
@@ -1923,7 +1859,7 @@
         <v>34</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O4" t="s">
         <v>40</v>
@@ -2223,7 +2159,7 @@
         <v>90</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E10" s="10">
         <v>46284</v>
@@ -2780,59 +2716,6 @@
       </c>
       <c r="R20" s="7" t="s">
         <v>128</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18">
-      <c r="A21" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" t="s">
-        <v>140</v>
-      </c>
-      <c r="C21" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" t="s">
-        <v>141</v>
-      </c>
-      <c r="G21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H21" t="str">
-        <f t="shared" si="1"/>
-        <v>بدون تاريخ</v>
-      </c>
-      <c r="I21" t="str">
-        <f t="shared" si="2"/>
-        <v>مراجعة مطلوبة</v>
-      </c>
-      <c r="J21" t="s">
-        <v>21</v>
-      </c>
-      <c r="K21" t="s">
-        <v>32</v>
-      </c>
-      <c r="L21" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="M21" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N21" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="O21" t="s">
-        <v>144</v>
-      </c>
-      <c r="P21" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>27</v>
-      </c>
-      <c r="R21" t="s">
-        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -2860,7 +2743,7 @@
     <row r="2" spans="1:2" ht="14.25" customHeight="1">
       <c r="A2" s="13"/>
       <c r="B2" s="15" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.25" customHeight="1">
@@ -2869,42 +2752,42 @@
     </row>
     <row r="4" spans="1:2" ht="14.25" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.25" customHeight="1">
       <c r="A5" s="13" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.25" customHeight="1">
       <c r="A6" s="13" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="14.25" customHeight="1">
       <c r="A7" s="13" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="14.25" customHeight="1">
       <c r="A8" s="13" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="14.25" customHeight="1">
@@ -2914,7 +2797,7 @@
     <row r="10" spans="1:2" ht="14.25" customHeight="1">
       <c r="A10" s="13"/>
       <c r="B10" s="16" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="14.25" customHeight="1">
@@ -2924,7 +2807,7 @@
     <row r="12" spans="1:2" ht="14.25" customHeight="1">
       <c r="A12" s="13"/>
       <c r="B12" s="16" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="14.25" customHeight="1">
@@ -2934,7 +2817,7 @@
     <row r="14" spans="1:2" ht="14.25" customHeight="1">
       <c r="A14" s="13"/>
       <c r="B14" s="16" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="14.25" customHeight="1">
@@ -2944,7 +2827,7 @@
     <row r="16" spans="1:2" ht="14.25" customHeight="1">
       <c r="A16" s="13"/>
       <c r="B16" s="16" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="14.25" customHeight="1">

--- a/Tracker_PowerBI_xlsx.xlsx
+++ b/Tracker_PowerBI_xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://meirc-my.sharepoint.com/personal/halzaben_meirc_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{A9DB5D68-FAF6-475D-815D-D63DA13F66D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2A48B39-E1C0-44A5-9812-E3D0BFEBD3C2}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{A9DB5D68-FAF6-475D-815D-D63DA13F66D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{670439F0-ADC7-4ACE-A674-7BFD5B0E33A7}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tracker_All" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="159">
   <si>
     <t>المصدر</t>
   </si>
@@ -818,13 +818,371 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
+    <t>3/2/2026</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RUQA7523 – </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>سعيد بن زيد، حي قرطبة، الرياض</t>
+    </r>
+  </si>
+  <si>
+    <t>COC Riyadh Chamber – CR42</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>رقم العضوية</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: 836599</t>
+    </r>
+  </si>
+  <si>
+    <t>16/07/2023</t>
+  </si>
+  <si>
+    <t>CoC 42 EXP Jan 6 2027.pdf</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CR: 1010860142 · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>درجة ثانية</t>
+    </r>
+  </si>
+  <si>
+    <t>CR 42</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">السجل التجاري – </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>CR42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>رقم السجل التجاري</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: 1010860142</t>
+    </r>
+  </si>
+  <si>
+    <t>08/02/2023</t>
+  </si>
+  <si>
+    <t>CR42-Center-1010860142.pdf</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>الرقم الوطني</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: 7033766317 · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">فرع شركة أجنبية </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>نشطة</t>
+    </r>
+  </si>
+  <si>
+    <t>Investment License</t>
+  </si>
+  <si>
+    <t>Ministry of Investment</t>
+  </si>
+  <si>
+    <t>Services Investment License</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ترخيص الاستثمار – </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>MISA</t>
+    </r>
+  </si>
+  <si>
+    <t>وزارة الاستثمار</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>رقم الترخيص</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: 102164308134617</t>
+    </r>
+  </si>
+  <si>
+    <t>13/03/2022</t>
+  </si>
+  <si>
+    <t>MISA (New) - 2027.pdf</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>الرقم الوطني</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: 7029908865</t>
+    </r>
+  </si>
+  <si>
+    <t>إقامة LINA AL ASHKAR</t>
+  </si>
+  <si>
+    <t>رقم الإقامة: 2598378632</t>
+  </si>
+  <si>
+    <t>إقامة MOHAMMED NAYAL</t>
+  </si>
+  <si>
+    <t>رقم الإقامة: 2572607188</t>
+  </si>
+  <si>
+    <t>National address 32</t>
+  </si>
+  <si>
+    <t>تأشيرة مريم ايهاب محمود احمد همام</t>
+  </si>
+  <si>
+    <t>MOSI Certificate</t>
+  </si>
+  <si>
+    <t>MOSI</t>
+  </si>
+  <si>
+    <t>SME – CR32</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>رقم الشهادة</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: 26265343654</t>
+    </r>
+  </si>
+  <si>
+    <t>SME - CR32.pdf</t>
+  </si>
+  <si>
+    <t>دليل استيراد Power BI</t>
+  </si>
+  <si>
+    <t>١</t>
+  </si>
+  <si>
+    <t>افتح Power BI Desktop → Home → Get Data → Excel Workbook</t>
+  </si>
+  <si>
+    <t>٢</t>
+  </si>
+  <si>
+    <t>اختر هذا الملف، ثم حدد ورقة Tracker_All فقط → Load</t>
+  </si>
+  <si>
+    <t>٣</t>
+  </si>
+  <si>
+    <t>Transform Data: تأكد أن عمود [تاريخ الانتهاء] نوعه Date</t>
+  </si>
+  <si>
+    <t>٤</t>
+  </si>
+  <si>
+    <t>تأكد أن [الأيام المتبقية] نوعه Whole Number</t>
+  </si>
+  <si>
+    <t>٥</t>
+  </si>
+  <si>
+    <t>أغلق Power Query Editor → Apply</t>
+  </si>
+  <si>
+    <t>المقاييس – انسخها من ملف DAX_Measures.txt</t>
+  </si>
+  <si>
+    <t>تصميم اللوحة – راجع ملف PowerBI_Design_Guide.pdf</t>
+  </si>
+  <si>
+    <t>تحديث البيانات: كلما عدّلت هذا الملف، اضغط Refresh في Power BI</t>
+  </si>
+  <si>
+    <t>مسار الملف: لا تغير اسم الملف أو مساره بعد ربطه بـ Power BI</t>
+  </si>
+  <si>
+    <t>GOSI 42</t>
+  </si>
+  <si>
+    <r>
+      <t>رقم الشهادة</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: 256343-19899920</t>
+    </r>
+  </si>
+  <si>
+    <t>Address Meirc Consulting Training</t>
+  </si>
+  <si>
+    <t>Address Meirc Training Center</t>
+  </si>
+  <si>
+    <r>
       <t>رقم الإثبات</t>
     </r>
     <r>
@@ -838,365 +1196,7 @@
     </r>
   </si>
   <si>
-    <t>3/2/2026</t>
-  </si>
-  <si>
-    <t>Meirc National Address updated Feb 2026.pdf</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">RUQA7523 – </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>سعيد بن زيد، حي قرطبة، الرياض</t>
-    </r>
-  </si>
-  <si>
-    <t>COC Riyadh Chamber – CR42</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>رقم العضوية</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 836599</t>
-    </r>
-  </si>
-  <si>
-    <t>16/07/2023</t>
-  </si>
-  <si>
-    <t>CoC 42 EXP Jan 6 2027.pdf</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CR: 1010860142 · </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>درجة ثانية</t>
-    </r>
-  </si>
-  <si>
-    <t>CR 42</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">السجل التجاري – </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>CR42</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>رقم السجل التجاري</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 1010860142</t>
-    </r>
-  </si>
-  <si>
-    <t>08/02/2023</t>
-  </si>
-  <si>
-    <t>CR42-Center-1010860142.pdf</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>الرقم الوطني</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: 7033766317 · </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">فرع شركة أجنبية </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>نشطة</t>
-    </r>
-  </si>
-  <si>
-    <t>Investment License</t>
-  </si>
-  <si>
-    <t>Ministry of Investment</t>
-  </si>
-  <si>
-    <t>Services Investment License</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ترخيص الاستثمار – </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>MISA</t>
-    </r>
-  </si>
-  <si>
-    <t>وزارة الاستثمار</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>رقم الترخيص</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 102164308134617</t>
-    </r>
-  </si>
-  <si>
-    <t>13/03/2022</t>
-  </si>
-  <si>
-    <t>MISA (New) - 2027.pdf</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>الرقم الوطني</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 7029908865</t>
-    </r>
-  </si>
-  <si>
-    <t>إقامة LINA AL ASHKAR</t>
-  </si>
-  <si>
-    <t>رقم الإقامة: 2598378632</t>
-  </si>
-  <si>
-    <t>إقامة MOHAMMED NAYAL</t>
-  </si>
-  <si>
-    <t>رقم الإقامة: 2572607188</t>
-  </si>
-  <si>
-    <t>National address 32</t>
-  </si>
-  <si>
-    <t>تأشيرة مريم ايهاب محمود احمد همام</t>
-  </si>
-  <si>
-    <t>MOSI Certificate</t>
-  </si>
-  <si>
-    <t>MOSI</t>
-  </si>
-  <si>
-    <t>SME – CR32</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>رقم الشهادة</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 26265343654</t>
-    </r>
-  </si>
-  <si>
-    <t>SME - CR32.pdf</t>
-  </si>
-  <si>
-    <t>دليل استيراد Power BI</t>
-  </si>
-  <si>
-    <t>١</t>
-  </si>
-  <si>
-    <t>افتح Power BI Desktop → Home → Get Data → Excel Workbook</t>
-  </si>
-  <si>
-    <t>٢</t>
-  </si>
-  <si>
-    <t>اختر هذا الملف، ثم حدد ورقة Tracker_All فقط → Load</t>
-  </si>
-  <si>
-    <t>٣</t>
-  </si>
-  <si>
-    <t>Transform Data: تأكد أن عمود [تاريخ الانتهاء] نوعه Date</t>
-  </si>
-  <si>
-    <t>٤</t>
-  </si>
-  <si>
-    <t>تأكد أن [الأيام المتبقية] نوعه Whole Number</t>
-  </si>
-  <si>
-    <t>٥</t>
-  </si>
-  <si>
-    <t>أغلق Power Query Editor → Apply</t>
-  </si>
-  <si>
-    <t>المقاييس – انسخها من ملف DAX_Measures.txt</t>
-  </si>
-  <si>
-    <t>تصميم اللوحة – راجع ملف PowerBI_Design_Guide.pdf</t>
-  </si>
-  <si>
-    <t>تحديث البيانات: كلما عدّلت هذا الملف، اضغط Refresh في Power BI</t>
-  </si>
-  <si>
-    <t>مسار الملف: لا تغير اسم الملف أو مساره بعد ربطه بـ Power BI</t>
-  </si>
-  <si>
-    <t>GOSI 42</t>
-  </si>
-  <si>
-    <r>
-      <t>رقم الشهادة</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 256343-19899920</t>
-    </r>
+    <t>رقم الإثبات: 1090961124</t>
   </si>
 </sst>
 </file>
@@ -1859,7 +1859,7 @@
         <v>34</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="O4" t="s">
         <v>40</v>
@@ -2159,7 +2159,7 @@
         <v>90</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E10" s="10">
         <v>46284</v>
@@ -2256,7 +2256,7 @@
         <v>101</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E12" s="10">
         <v>46419</v>
@@ -2288,19 +2288,19 @@
         <v>104</v>
       </c>
       <c r="N12" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="O12" t="s">
         <v>105</v>
       </c>
-      <c r="O12" t="s">
-        <v>106</v>
-      </c>
       <c r="P12" t="s">
-        <v>107</v>
+        <v>155</v>
       </c>
       <c r="Q12" t="s">
         <v>42</v>
       </c>
       <c r="R12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="14.25" customHeight="1">
@@ -2346,19 +2346,19 @@
         <v>104</v>
       </c>
       <c r="N13" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="O13" t="s">
         <v>105</v>
       </c>
-      <c r="O13" t="s">
-        <v>106</v>
-      </c>
       <c r="P13" t="s">
-        <v>107</v>
+        <v>156</v>
       </c>
       <c r="Q13" t="s">
         <v>42</v>
       </c>
       <c r="R13" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="14.25" customHeight="1">
@@ -2372,7 +2372,7 @@
         <v>45</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E14" s="10">
         <v>46391</v>
@@ -2406,19 +2406,19 @@
         <v>48</v>
       </c>
       <c r="N14" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="O14" t="s">
+        <v>109</v>
+      </c>
+      <c r="P14" t="s">
         <v>110</v>
-      </c>
-      <c r="O14" t="s">
-        <v>111</v>
-      </c>
-      <c r="P14" t="s">
-        <v>112</v>
       </c>
       <c r="Q14" t="s">
         <v>42</v>
       </c>
       <c r="R14" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="24.75" customHeight="1">
@@ -2432,7 +2432,7 @@
         <v>54</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E15" s="10">
         <v>46391</v>
@@ -2460,25 +2460,25 @@
         <v>56</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="M15" s="7" t="s">
         <v>58</v>
       </c>
       <c r="N15" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="O15" t="s">
+        <v>115</v>
+      </c>
+      <c r="P15" t="s">
         <v>116</v>
-      </c>
-      <c r="O15" t="s">
-        <v>117</v>
-      </c>
-      <c r="P15" t="s">
-        <v>118</v>
       </c>
       <c r="Q15" t="s">
         <v>42</v>
       </c>
       <c r="R15" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="14.25" customHeight="1">
@@ -2486,13 +2486,13 @@
         <v>18</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>122</v>
       </c>
       <c r="E16" s="10">
         <v>46396</v>
@@ -2520,25 +2520,25 @@
         <v>32</v>
       </c>
       <c r="L16" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="N16" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="M16" s="7" t="s">
+      <c r="O16" t="s">
         <v>124</v>
       </c>
-      <c r="N16" s="7" t="s">
+      <c r="P16" t="s">
         <v>125</v>
-      </c>
-      <c r="O16" t="s">
-        <v>126</v>
-      </c>
-      <c r="P16" t="s">
-        <v>127</v>
       </c>
       <c r="Q16" t="s">
         <v>27</v>
       </c>
       <c r="R16" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="14.25" customHeight="1">
@@ -2552,7 +2552,7 @@
         <v>87</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E17" s="10">
         <v>46535</v>
@@ -2577,7 +2577,7 @@
         <v>72</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="14.25" customHeight="1">
@@ -2591,7 +2591,7 @@
         <v>97</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E18" s="10">
         <v>46554</v>
@@ -2616,7 +2616,7 @@
         <v>72</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="14.25" customHeight="1">
@@ -2624,13 +2624,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E19" s="10">
         <v>46398</v>
@@ -2669,7 +2669,7 @@
         <v>79</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E20" s="9">
         <v>46526</v>
@@ -2703,19 +2703,19 @@
         <v>82</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="O20" t="s">
         <v>84</v>
       </c>
       <c r="P20" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="Q20" t="s">
         <v>27</v>
       </c>
       <c r="R20" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -2743,7 +2743,7 @@
     <row r="2" spans="1:2" ht="14.25" customHeight="1">
       <c r="A2" s="13"/>
       <c r="B2" s="15" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.25" customHeight="1">
@@ -2752,42 +2752,42 @@
     </row>
     <row r="4" spans="1:2" ht="14.25" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.25" customHeight="1">
       <c r="A5" s="13" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.25" customHeight="1">
       <c r="A6" s="13" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="14.25" customHeight="1">
       <c r="A7" s="13" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="14.25" customHeight="1">
       <c r="A8" s="13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="14.25" customHeight="1">
@@ -2797,7 +2797,7 @@
     <row r="10" spans="1:2" ht="14.25" customHeight="1">
       <c r="A10" s="13"/>
       <c r="B10" s="16" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="14.25" customHeight="1">
@@ -2807,7 +2807,7 @@
     <row r="12" spans="1:2" ht="14.25" customHeight="1">
       <c r="A12" s="13"/>
       <c r="B12" s="16" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="14.25" customHeight="1">
@@ -2817,7 +2817,7 @@
     <row r="14" spans="1:2" ht="14.25" customHeight="1">
       <c r="A14" s="13"/>
       <c r="B14" s="16" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="14.25" customHeight="1">
@@ -2827,7 +2827,7 @@
     <row r="16" spans="1:2" ht="14.25" customHeight="1">
       <c r="A16" s="13"/>
       <c r="B16" s="16" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="14.25" customHeight="1">
@@ -2880,7 +2880,7 @@
         <v>75</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E20" s="10">
         <v>46215</v>

--- a/Tracker_PowerBI_xlsx.xlsx
+++ b/Tracker_PowerBI_xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://meirc-my.sharepoint.com/personal/halzaben_meirc_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{A9DB5D68-FAF6-475D-815D-D63DA13F66D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{670439F0-ADC7-4ACE-A674-7BFD5B0E33A7}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{A9DB5D68-FAF6-475D-815D-D63DA13F66D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8DBEEC2-28AA-48F2-8239-7F356D162855}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tracker_All" sheetId="1" r:id="rId1"/>
@@ -1176,12 +1176,6 @@
     </r>
   </si>
   <si>
-    <t>Address Meirc Consulting Training</t>
-  </si>
-  <si>
-    <t>Address Meirc Training Center</t>
-  </si>
-  <si>
     <r>
       <t>رقم الإثبات</t>
     </r>
@@ -1197,6 +1191,12 @@
   </si>
   <si>
     <t>رقم الإثبات: 1090961124</t>
+  </si>
+  <si>
+    <t>Address Meirc Consulting Training.pdf</t>
+  </si>
+  <si>
+    <t>Address Meirc Training Center.pdf</t>
   </si>
 </sst>
 </file>
@@ -2288,16 +2288,16 @@
         <v>104</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="O12" t="s">
         <v>105</v>
       </c>
       <c r="P12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q12" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="R12" t="s">
         <v>106</v>
@@ -2346,13 +2346,13 @@
         <v>104</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O13" t="s">
         <v>105</v>
       </c>
       <c r="P13" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q13" t="s">
         <v>42</v>

--- a/Tracker_PowerBI_xlsx.xlsx
+++ b/Tracker_PowerBI_xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://meirc-my.sharepoint.com/personal/halzaben_meirc_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{A9DB5D68-FAF6-475D-815D-D63DA13F66D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8DBEEC2-28AA-48F2-8239-7F356D162855}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{A9DB5D68-FAF6-475D-815D-D63DA13F66D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B842E2E-240F-4F38-BEE2-12C0CCF680FD}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="162">
   <si>
     <t>المصدر</t>
   </si>
@@ -1197,6 +1197,26 @@
   </si>
   <si>
     <t>Address Meirc Training Center.pdf</t>
+  </si>
+  <si>
+    <t>VAT</t>
+  </si>
+  <si>
+    <r>
+      <t>رقم الشهادة</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: 100261180389068</t>
+    </r>
+  </si>
+  <si>
+    <t>VAT - cert.pdf</t>
   </si>
 </sst>
 </file>
@@ -1623,7 +1643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2716,6 +2736,103 @@
       </c>
       <c r="R20" s="7" t="s">
         <v>126</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="14.25" customHeight="1">
+      <c r="A21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E21" s="4"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="4" t="str">
+        <f t="shared" ref="G21:G22" si="5">IF(E21="","",E21-30)</f>
+        <v/>
+      </c>
+      <c r="H21" s="6" t="str">
+        <f t="shared" ref="H21:H22" si="6">IF(E21="","بدون تاريخ",IF(F21&lt;0,"منتهي",IF(F21&lt;=30,"حرج",IF(F21&lt;=60,"قريب","ساري"))))</f>
+        <v>بدون تاريخ</v>
+      </c>
+      <c r="I21" s="6" t="str">
+        <f t="shared" ref="I21:I22" si="7">IF(H21="بدون تاريخ","مراجعة مطلوبة",IF(H21="منتهي","عالية",IF(H21="حرج","عالية",IF(H21="قريب","متوسطة","منخفضة"))))</f>
+        <v>مراجعة مطلوبة</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" s="3"/>
+      <c r="L21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="P21" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>27</v>
+      </c>
+      <c r="R21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="14.25" customHeight="1">
+      <c r="A22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H22" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v>بدون تاريخ</v>
+      </c>
+      <c r="I22" s="6" t="str">
+        <f t="shared" si="7"/>
+        <v>مراجعة مطلوبة</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" s="3"/>
+      <c r="L22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="P22" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/Tracker_PowerBI_xlsx.xlsx
+++ b/Tracker_PowerBI_xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://meirc-my.sharepoint.com/personal/halzaben_meirc_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{A9DB5D68-FAF6-475D-815D-D63DA13F66D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B842E2E-240F-4F38-BEE2-12C0CCF680FD}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{A9DB5D68-FAF6-475D-815D-D63DA13F66D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F5D5E43-C8CA-4422-9EAC-D82602DF33A5}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tracker_All" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="163">
   <si>
     <t>المصدر</t>
   </si>
@@ -1217,6 +1217,20 @@
   </si>
   <si>
     <t>VAT - cert.pdf</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">شهادة تسجيل في ضريبة القيمة المضافة  – </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>VAT Registration Certificate</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -2770,7 +2784,7 @@
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="7" t="s">
-        <v>22</v>
+        <v>162</v>
       </c>
       <c r="M21" s="7" t="s">
         <v>23</v>
@@ -2820,7 +2834,7 @@
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="7" t="s">
-        <v>22</v>
+        <v>162</v>
       </c>
       <c r="M22" s="7" t="s">
         <v>23</v>

--- a/Tracker_PowerBI_xlsx.xlsx
+++ b/Tracker_PowerBI_xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://meirc-my.sharepoint.com/personal/halzaben_meirc_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{A9DB5D68-FAF6-475D-815D-D63DA13F66D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F5D5E43-C8CA-4422-9EAC-D82602DF33A5}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{A9DB5D68-FAF6-475D-815D-D63DA13F66D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D0A576F-D93B-4396-9DDD-DFA866174C92}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tracker_All" sheetId="1" r:id="rId1"/>
@@ -722,13 +722,486 @@
     <t>المؤسسة العامة للتأمينات الاجتماعية</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
+    <t>11/04/2026</t>
+  </si>
+  <si>
+    <t>MOHAMMED NAYAL</t>
+  </si>
+  <si>
+    <t>تأشيرة MOHAMMED NAYAL</t>
+  </si>
+  <si>
+    <t>حالة التأشيرة: مستعمل</t>
+  </si>
+  <si>
+    <t>National Address Record</t>
+  </si>
+  <si>
+    <t>SPL</t>
+  </si>
+  <si>
+    <t>National address 42</t>
+  </si>
+  <si>
+    <t>العنوان الوطني</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">البريد السعودي </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>SPL</t>
+    </r>
+  </si>
+  <si>
+    <t>3/2/2026</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RUQA7523 – </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>سعيد بن زيد، حي قرطبة، الرياض</t>
+    </r>
+  </si>
+  <si>
+    <t>COC Riyadh Chamber – CR42</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>رقم العضوية</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: 836599</t>
+    </r>
+  </si>
+  <si>
+    <t>16/07/2023</t>
+  </si>
+  <si>
+    <t>CoC 42 EXP Jan 6 2027.pdf</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CR: 1010860142 · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>درجة ثانية</t>
+    </r>
+  </si>
+  <si>
+    <t>CR 42</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">السجل التجاري – </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>CR42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>رقم السجل التجاري</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: 1010860142</t>
+    </r>
+  </si>
+  <si>
+    <t>08/02/2023</t>
+  </si>
+  <si>
+    <t>CR42-Center-1010860142.pdf</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>الرقم الوطني</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: 7033766317 · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">فرع شركة أجنبية </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>نشطة</t>
+    </r>
+  </si>
+  <si>
+    <t>Investment License</t>
+  </si>
+  <si>
+    <t>Ministry of Investment</t>
+  </si>
+  <si>
+    <t>Services Investment License</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ترخيص الاستثمار – </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>MISA</t>
+    </r>
+  </si>
+  <si>
+    <t>وزارة الاستثمار</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>رقم الترخيص</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: 102164308134617</t>
+    </r>
+  </si>
+  <si>
+    <t>13/03/2022</t>
+  </si>
+  <si>
+    <t>MISA (New) - 2027.pdf</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>الرقم الوطني</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: 7029908865</t>
+    </r>
+  </si>
+  <si>
+    <t>إقامة LINA AL ASHKAR</t>
+  </si>
+  <si>
+    <t>رقم الإقامة: 2598378632</t>
+  </si>
+  <si>
+    <t>إقامة MOHAMMED NAYAL</t>
+  </si>
+  <si>
+    <t>رقم الإقامة: 2572607188</t>
+  </si>
+  <si>
+    <t>National address 32</t>
+  </si>
+  <si>
+    <t>تأشيرة مريم ايهاب محمود احمد همام</t>
+  </si>
+  <si>
+    <t>MOSI Certificate</t>
+  </si>
+  <si>
+    <t>MOSI</t>
+  </si>
+  <si>
+    <t>SME – CR32</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>رقم الشهادة</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: 26265343654</t>
+    </r>
+  </si>
+  <si>
+    <t>SME - CR32.pdf</t>
+  </si>
+  <si>
+    <t>دليل استيراد Power BI</t>
+  </si>
+  <si>
+    <t>١</t>
+  </si>
+  <si>
+    <t>افتح Power BI Desktop → Home → Get Data → Excel Workbook</t>
+  </si>
+  <si>
+    <t>٢</t>
+  </si>
+  <si>
+    <t>اختر هذا الملف، ثم حدد ورقة Tracker_All فقط → Load</t>
+  </si>
+  <si>
+    <t>٣</t>
+  </si>
+  <si>
+    <t>Transform Data: تأكد أن عمود [تاريخ الانتهاء] نوعه Date</t>
+  </si>
+  <si>
+    <t>٤</t>
+  </si>
+  <si>
+    <t>تأكد أن [الأيام المتبقية] نوعه Whole Number</t>
+  </si>
+  <si>
+    <t>٥</t>
+  </si>
+  <si>
+    <t>أغلق Power Query Editor → Apply</t>
+  </si>
+  <si>
+    <t>المقاييس – انسخها من ملف DAX_Measures.txt</t>
+  </si>
+  <si>
+    <t>تصميم اللوحة – راجع ملف PowerBI_Design_Guide.pdf</t>
+  </si>
+  <si>
+    <t>تحديث البيانات: كلما عدّلت هذا الملف، اضغط Refresh في Power BI</t>
+  </si>
+  <si>
+    <t>مسار الملف: لا تغير اسم الملف أو مساره بعد ربطه بـ Power BI</t>
+  </si>
+  <si>
+    <t>GOSI 42</t>
+  </si>
+  <si>
+    <r>
+      <t>رقم الشهادة</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: 256343-19899920</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>رقم الإثبات</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: 1080130933</t>
+    </r>
+  </si>
+  <si>
+    <t>رقم الإثبات: 1090961124</t>
+  </si>
+  <si>
+    <t>Address Meirc Consulting Training.pdf</t>
+  </si>
+  <si>
+    <t>Address Meirc Training Center.pdf</t>
+  </si>
+  <si>
+    <t>VAT</t>
+  </si>
+  <si>
+    <r>
+      <t>رقم الشهادة</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: 100261180389068</t>
+    </r>
+  </si>
+  <si>
+    <t>VAT - cert.pdf</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">شهادة تسجيل في ضريبة القيمة المضافة  – </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>VAT Registration Certificate</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>GOSI CR42 11-25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>.pdf</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t>رمز الشهادة</t>
     </r>
     <r>
@@ -738,23 +1211,11 @@
         <rFont val="Calibri"/>
         <charset val="1"/>
       </rPr>
-      <t>: 112057702</t>
-    </r>
-  </si>
-  <si>
-    <t>11/04/2026</t>
-  </si>
-  <si>
-    <t>GOSI.pdf</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
+      <t>: 119567603</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t>رقم الاشتراك</t>
     </r>
     <r>
@@ -764,7 +1225,7 @@
         <rFont val="Calibri"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: 638909642 · 10 </t>
+      <t xml:space="preserve">: 638909642 · 9 </t>
     </r>
     <r>
       <rPr>
@@ -774,462 +1235,6 @@
         <family val="2"/>
       </rPr>
       <t>مشتركين</t>
-    </r>
-  </si>
-  <si>
-    <t>MOHAMMED NAYAL</t>
-  </si>
-  <si>
-    <t>تأشيرة MOHAMMED NAYAL</t>
-  </si>
-  <si>
-    <t>حالة التأشيرة: مستعمل</t>
-  </si>
-  <si>
-    <t>National Address Record</t>
-  </si>
-  <si>
-    <t>SPL</t>
-  </si>
-  <si>
-    <t>National address 42</t>
-  </si>
-  <si>
-    <t>العنوان الوطني</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">البريد السعودي </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>SPL</t>
-    </r>
-  </si>
-  <si>
-    <t>3/2/2026</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">RUQA7523 – </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>سعيد بن زيد، حي قرطبة، الرياض</t>
-    </r>
-  </si>
-  <si>
-    <t>COC Riyadh Chamber – CR42</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>رقم العضوية</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 836599</t>
-    </r>
-  </si>
-  <si>
-    <t>16/07/2023</t>
-  </si>
-  <si>
-    <t>CoC 42 EXP Jan 6 2027.pdf</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CR: 1010860142 · </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>درجة ثانية</t>
-    </r>
-  </si>
-  <si>
-    <t>CR 42</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">السجل التجاري – </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>CR42</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>رقم السجل التجاري</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 1010860142</t>
-    </r>
-  </si>
-  <si>
-    <t>08/02/2023</t>
-  </si>
-  <si>
-    <t>CR42-Center-1010860142.pdf</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>الرقم الوطني</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: 7033766317 · </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">فرع شركة أجنبية </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>نشطة</t>
-    </r>
-  </si>
-  <si>
-    <t>Investment License</t>
-  </si>
-  <si>
-    <t>Ministry of Investment</t>
-  </si>
-  <si>
-    <t>Services Investment License</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ترخيص الاستثمار – </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>MISA</t>
-    </r>
-  </si>
-  <si>
-    <t>وزارة الاستثمار</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>رقم الترخيص</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 102164308134617</t>
-    </r>
-  </si>
-  <si>
-    <t>13/03/2022</t>
-  </si>
-  <si>
-    <t>MISA (New) - 2027.pdf</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>الرقم الوطني</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 7029908865</t>
-    </r>
-  </si>
-  <si>
-    <t>إقامة LINA AL ASHKAR</t>
-  </si>
-  <si>
-    <t>رقم الإقامة: 2598378632</t>
-  </si>
-  <si>
-    <t>إقامة MOHAMMED NAYAL</t>
-  </si>
-  <si>
-    <t>رقم الإقامة: 2572607188</t>
-  </si>
-  <si>
-    <t>National address 32</t>
-  </si>
-  <si>
-    <t>تأشيرة مريم ايهاب محمود احمد همام</t>
-  </si>
-  <si>
-    <t>MOSI Certificate</t>
-  </si>
-  <si>
-    <t>MOSI</t>
-  </si>
-  <si>
-    <t>SME – CR32</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>رقم الشهادة</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 26265343654</t>
-    </r>
-  </si>
-  <si>
-    <t>SME - CR32.pdf</t>
-  </si>
-  <si>
-    <t>دليل استيراد Power BI</t>
-  </si>
-  <si>
-    <t>١</t>
-  </si>
-  <si>
-    <t>افتح Power BI Desktop → Home → Get Data → Excel Workbook</t>
-  </si>
-  <si>
-    <t>٢</t>
-  </si>
-  <si>
-    <t>اختر هذا الملف، ثم حدد ورقة Tracker_All فقط → Load</t>
-  </si>
-  <si>
-    <t>٣</t>
-  </si>
-  <si>
-    <t>Transform Data: تأكد أن عمود [تاريخ الانتهاء] نوعه Date</t>
-  </si>
-  <si>
-    <t>٤</t>
-  </si>
-  <si>
-    <t>تأكد أن [الأيام المتبقية] نوعه Whole Number</t>
-  </si>
-  <si>
-    <t>٥</t>
-  </si>
-  <si>
-    <t>أغلق Power Query Editor → Apply</t>
-  </si>
-  <si>
-    <t>المقاييس – انسخها من ملف DAX_Measures.txt</t>
-  </si>
-  <si>
-    <t>تصميم اللوحة – راجع ملف PowerBI_Design_Guide.pdf</t>
-  </si>
-  <si>
-    <t>تحديث البيانات: كلما عدّلت هذا الملف، اضغط Refresh في Power BI</t>
-  </si>
-  <si>
-    <t>مسار الملف: لا تغير اسم الملف أو مساره بعد ربطه بـ Power BI</t>
-  </si>
-  <si>
-    <t>GOSI 42</t>
-  </si>
-  <si>
-    <r>
-      <t>رقم الشهادة</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 256343-19899920</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>رقم الإثبات</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 1080130933</t>
-    </r>
-  </si>
-  <si>
-    <t>رقم الإثبات: 1090961124</t>
-  </si>
-  <si>
-    <t>Address Meirc Consulting Training.pdf</t>
-  </si>
-  <si>
-    <t>Address Meirc Training Center.pdf</t>
-  </si>
-  <si>
-    <t>VAT</t>
-  </si>
-  <si>
-    <r>
-      <t>رقم الشهادة</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 100261180389068</t>
-    </r>
-  </si>
-  <si>
-    <t>VAT - cert.pdf</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">شهادة تسجيل في ضريبة القيمة المضافة  – </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>VAT Registration Certificate</t>
     </r>
   </si>
 </sst>
@@ -1240,7 +1245,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1297,6 +1302,12 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1364,7 +1375,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1410,6 +1421,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1748,7 +1760,7 @@
       </c>
       <c r="F2" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G2" s="4">
         <f t="shared" ref="G2:G20" si="0">IF(E2="","",E2-30)</f>
@@ -1806,7 +1818,7 @@
       </c>
       <c r="F3" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G3" s="4">
         <f t="shared" si="0"/>
@@ -1866,7 +1878,7 @@
       </c>
       <c r="F4" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
@@ -1893,7 +1905,7 @@
         <v>34</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="O4" t="s">
         <v>40</v>
@@ -1926,7 +1938,7 @@
       </c>
       <c r="F5" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G5" s="4">
         <f t="shared" si="0"/>
@@ -1986,7 +1998,7 @@
       </c>
       <c r="F6" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G6" s="4">
         <f t="shared" si="0"/>
@@ -2046,7 +2058,7 @@
       </c>
       <c r="F7" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="G7" s="4">
         <f t="shared" si="0"/>
@@ -2101,7 +2113,7 @@
       </c>
       <c r="F8" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="0"/>
@@ -2161,7 +2173,7 @@
       </c>
       <c r="F9" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G9" s="4">
         <f t="shared" si="0"/>
@@ -2193,26 +2205,26 @@
         <v>90</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E10" s="10">
-        <v>46284</v>
+        <v>46351</v>
       </c>
       <c r="F10" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>27</v>
+        <v>91</v>
       </c>
       <c r="G10" s="4">
         <f t="shared" si="0"/>
-        <v>46254</v>
+        <v>46321</v>
       </c>
       <c r="H10" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>حرج</v>
+        <v>ساري</v>
       </c>
       <c r="I10" s="6" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>عالية</v>
+        <v>منخفضة</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>21</v>
@@ -2225,19 +2237,19 @@
         <v>92</v>
       </c>
       <c r="N10" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="O10" t="s">
         <v>93</v>
       </c>
-      <c r="O10" t="s">
-        <v>94</v>
-      </c>
-      <c r="P10" t="s">
-        <v>95</v>
+      <c r="P10" s="17" t="s">
+        <v>160</v>
       </c>
       <c r="Q10" t="s">
         <v>42</v>
       </c>
       <c r="R10" s="7" t="s">
-        <v>96</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="14.25" customHeight="1">
@@ -2248,17 +2260,17 @@
         <v>71</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E11" s="10">
         <v>46469</v>
       </c>
       <c r="F11" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G11" s="4">
         <f t="shared" si="0"/>
@@ -2276,7 +2288,7 @@
         <v>72</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="14.25" customHeight="1">
@@ -2284,20 +2296,20 @@
         <v>18</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E12" s="10">
         <v>46419</v>
       </c>
       <c r="F12" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G12" s="4">
         <f t="shared" ref="G12" si="3">IF(E12="","",E12-30)</f>
@@ -2316,25 +2328,25 @@
       </c>
       <c r="K12" s="6"/>
       <c r="L12" s="7" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="O12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="P12" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="Q12" t="s">
         <v>27</v>
       </c>
       <c r="R12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="14.25" customHeight="1">
@@ -2342,20 +2354,20 @@
         <v>18</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E13" s="10">
         <v>46419</v>
       </c>
       <c r="F13" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="0"/>
@@ -2374,25 +2386,25 @@
       </c>
       <c r="K13" s="6"/>
       <c r="L13" s="7" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="N13" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="O13" t="s">
+        <v>102</v>
+      </c>
+      <c r="P13" t="s">
         <v>155</v>
-      </c>
-      <c r="O13" t="s">
-        <v>105</v>
-      </c>
-      <c r="P13" t="s">
-        <v>158</v>
       </c>
       <c r="Q13" t="s">
         <v>42</v>
       </c>
       <c r="R13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="14.25" customHeight="1">
@@ -2406,14 +2418,14 @@
         <v>45</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E14" s="10">
         <v>46391</v>
       </c>
       <c r="F14" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" si="0"/>
@@ -2440,19 +2452,19 @@
         <v>48</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="O14" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="P14" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="Q14" t="s">
         <v>42</v>
       </c>
       <c r="R14" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="24.75" customHeight="1">
@@ -2466,14 +2478,14 @@
         <v>54</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E15" s="10">
         <v>46391</v>
       </c>
       <c r="F15" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G15" s="4">
         <f t="shared" si="0"/>
@@ -2494,25 +2506,25 @@
         <v>56</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="M15" s="7" t="s">
         <v>58</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="O15" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="Q15" t="s">
         <v>42</v>
       </c>
       <c r="R15" s="7" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="14.25" customHeight="1">
@@ -2520,20 +2532,20 @@
         <v>18</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E16" s="10">
         <v>46396</v>
       </c>
       <c r="F16" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G16" s="4">
         <f t="shared" si="0"/>
@@ -2554,25 +2566,25 @@
         <v>32</v>
       </c>
       <c r="L16" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="O16" t="s">
         <v>121</v>
       </c>
-      <c r="M16" s="7" t="s">
+      <c r="P16" t="s">
         <v>122</v>
-      </c>
-      <c r="N16" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="O16" t="s">
-        <v>124</v>
-      </c>
-      <c r="P16" t="s">
-        <v>125</v>
       </c>
       <c r="Q16" t="s">
         <v>27</v>
       </c>
       <c r="R16" s="7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="14.25" customHeight="1">
@@ -2586,14 +2598,14 @@
         <v>87</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E17" s="10">
         <v>46535</v>
       </c>
       <c r="F17" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="G17" s="4">
         <f t="shared" si="0"/>
@@ -2611,7 +2623,7 @@
         <v>72</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="14.25" customHeight="1">
@@ -2622,17 +2634,17 @@
         <v>74</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E18" s="10">
         <v>46554</v>
       </c>
       <c r="F18" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G18" s="4">
         <f t="shared" si="0"/>
@@ -2650,7 +2662,7 @@
         <v>72</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="14.25" customHeight="1">
@@ -2658,20 +2670,20 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E19" s="10">
         <v>46398</v>
       </c>
       <c r="F19" s="5">
         <f ca="1">E19-TODAY()</f>
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G19" s="4">
         <f t="shared" si="0"/>
@@ -2703,14 +2715,14 @@
         <v>79</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E20" s="9">
         <v>46526</v>
       </c>
       <c r="F20" s="5">
         <f ca="1">E20-TODAY()</f>
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G20" s="4">
         <f t="shared" si="0"/>
@@ -2737,19 +2749,19 @@
         <v>82</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="O20" t="s">
         <v>84</v>
       </c>
       <c r="P20" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="Q20" t="s">
         <v>27</v>
       </c>
       <c r="R20" s="7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="14.25" customHeight="1">
@@ -2757,13 +2769,13 @@
         <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>19</v>
+        <v>156</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="5"/>
@@ -2784,16 +2796,16 @@
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="7" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="M21" s="7" t="s">
         <v>23</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="P21" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q21" t="s">
         <v>27</v>
@@ -2807,13 +2819,13 @@
         <v>18</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>19</v>
+        <v>156</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="5"/>
@@ -2834,16 +2846,16 @@
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="7" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="M22" s="7" t="s">
         <v>23</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="P22" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q22" t="s">
         <v>42</v>
@@ -2874,7 +2886,7 @@
     <row r="2" spans="1:2" ht="14.25" customHeight="1">
       <c r="A2" s="13"/>
       <c r="B2" s="15" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.25" customHeight="1">
@@ -2883,42 +2895,42 @@
     </row>
     <row r="4" spans="1:2" ht="14.25" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.25" customHeight="1">
       <c r="A5" s="13" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.25" customHeight="1">
       <c r="A6" s="13" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="14.25" customHeight="1">
       <c r="A7" s="13" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="14.25" customHeight="1">
       <c r="A8" s="13" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="14.25" customHeight="1">
@@ -2928,7 +2940,7 @@
     <row r="10" spans="1:2" ht="14.25" customHeight="1">
       <c r="A10" s="13"/>
       <c r="B10" s="16" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="14.25" customHeight="1">
@@ -2938,7 +2950,7 @@
     <row r="12" spans="1:2" ht="14.25" customHeight="1">
       <c r="A12" s="13"/>
       <c r="B12" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="14.25" customHeight="1">
@@ -2948,7 +2960,7 @@
     <row r="14" spans="1:2" ht="14.25" customHeight="1">
       <c r="A14" s="13"/>
       <c r="B14" s="16" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="14.25" customHeight="1">
@@ -2958,7 +2970,7 @@
     <row r="16" spans="1:2" ht="14.25" customHeight="1">
       <c r="A16" s="13"/>
       <c r="B16" s="16" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="14.25" customHeight="1">
@@ -3011,7 +3023,7 @@
         <v>75</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E20" s="10">
         <v>46215</v>

--- a/Tracker_PowerBI_xlsx.xlsx
+++ b/Tracker_PowerBI_xlsx.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://meirc-my.sharepoint.com/personal/halzaben_meirc_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{A9DB5D68-FAF6-475D-815D-D63DA13F66D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D0A576F-D93B-4396-9DDD-DFA866174C92}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{A9DB5D68-FAF6-475D-815D-D63DA13F66D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{705BACDB-8E5F-4650-BD7D-CAE6854CD977}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="167">
   <si>
     <t>المصدر</t>
   </si>
@@ -1147,40 +1147,6 @@
     <t>Address Meirc Training Center.pdf</t>
   </si>
   <si>
-    <t>VAT</t>
-  </si>
-  <si>
-    <r>
-      <t>رقم الشهادة</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 100261180389068</t>
-    </r>
-  </si>
-  <si>
-    <t>VAT - cert.pdf</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">شهادة تسجيل في ضريبة القيمة المضافة  – </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>VAT Registration Certificate</t>
-    </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1236,6 +1202,30 @@
       </rPr>
       <t>مشتركين</t>
     </r>
+  </si>
+  <si>
+    <t>رقم الشهادة : 318666 M</t>
+  </si>
+  <si>
+    <t>Local Content Certificate.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 318666 M</t>
+  </si>
+  <si>
+    <t>هيئة المحتوى المحلي والمشتريات الحكومية</t>
+  </si>
+  <si>
+    <t>شهادة المحتوى المحلي - Local Content Certificate</t>
+  </si>
+  <si>
+    <t>Local Content &amp; Government Procurement Authority</t>
+  </si>
+  <si>
+    <t>Local Content Certificate</t>
+  </si>
+  <si>
+    <t>Local Content</t>
   </si>
 </sst>
 </file>
@@ -1669,7 +1659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1760,7 +1750,7 @@
       </c>
       <c r="F2" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="G2" s="4">
         <f t="shared" ref="G2:G20" si="0">IF(E2="","",E2-30)</f>
@@ -1818,7 +1808,7 @@
       </c>
       <c r="F3" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G3" s="4">
         <f t="shared" si="0"/>
@@ -1826,11 +1816,11 @@
       </c>
       <c r="H3" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>قريب</v>
+        <v>حرج</v>
       </c>
       <c r="I3" s="6" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>متوسطة</v>
+        <v>عالية</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>21</v>
@@ -1878,7 +1868,7 @@
       </c>
       <c r="F4" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
@@ -1886,11 +1876,11 @@
       </c>
       <c r="H4" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>قريب</v>
+        <v>حرج</v>
       </c>
       <c r="I4" s="6" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>متوسطة</v>
+        <v>عالية</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>21</v>
@@ -1938,7 +1928,7 @@
       </c>
       <c r="F5" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="G5" s="4">
         <f t="shared" si="0"/>
@@ -1998,7 +1988,7 @@
       </c>
       <c r="F6" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="G6" s="4">
         <f t="shared" si="0"/>
@@ -2058,7 +2048,7 @@
       </c>
       <c r="F7" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="G7" s="4">
         <f t="shared" si="0"/>
@@ -2113,7 +2103,7 @@
       </c>
       <c r="F8" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="0"/>
@@ -2173,7 +2163,7 @@
       </c>
       <c r="F9" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="G9" s="4">
         <f t="shared" si="0"/>
@@ -2212,7 +2202,7 @@
       </c>
       <c r="F10" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="G10" s="4">
         <f t="shared" si="0"/>
@@ -2237,19 +2227,19 @@
         <v>92</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="O10" t="s">
         <v>93</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="Q10" t="s">
         <v>42</v>
       </c>
       <c r="R10" s="7" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="14.25" customHeight="1">
@@ -2270,7 +2260,7 @@
       </c>
       <c r="F11" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="G11" s="4">
         <f t="shared" si="0"/>
@@ -2309,7 +2299,7 @@
       </c>
       <c r="F12" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G12" s="4">
         <f t="shared" ref="G12" si="3">IF(E12="","",E12-30)</f>
@@ -2367,7 +2357,7 @@
       </c>
       <c r="F13" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="0"/>
@@ -2425,7 +2415,7 @@
       </c>
       <c r="F14" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" si="0"/>
@@ -2485,7 +2475,7 @@
       </c>
       <c r="F15" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="G15" s="4">
         <f t="shared" si="0"/>
@@ -2545,7 +2535,7 @@
       </c>
       <c r="F16" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="G16" s="4">
         <f t="shared" si="0"/>
@@ -2605,7 +2595,7 @@
       </c>
       <c r="F17" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="G17" s="4">
         <f t="shared" si="0"/>
@@ -2644,7 +2634,7 @@
       </c>
       <c r="F18" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="G18" s="4">
         <f t="shared" si="0"/>
@@ -2683,7 +2673,7 @@
       </c>
       <c r="F19" s="5">
         <f ca="1">E19-TODAY()</f>
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="G19" s="4">
         <f t="shared" si="0"/>
@@ -2722,7 +2712,7 @@
       </c>
       <c r="F20" s="5">
         <f ca="1">E20-TODAY()</f>
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="G20" s="4">
         <f t="shared" si="0"/>
@@ -2769,96 +2759,54 @@
         <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>20</v>
+        <v>164</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="E21" s="4"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="4" t="str">
-        <f t="shared" ref="G21:G22" si="5">IF(E21="","",E21-30)</f>
-        <v/>
-      </c>
-      <c r="H21" s="6" t="str">
-        <f t="shared" ref="H21:H22" si="6">IF(E21="","بدون تاريخ",IF(F21&lt;0,"منتهي",IF(F21&lt;=30,"حرج",IF(F21&lt;=60,"قريب","ساري"))))</f>
-        <v>بدون تاريخ</v>
-      </c>
-      <c r="I21" s="6" t="str">
-        <f t="shared" ref="I21:I22" si="7">IF(H21="بدون تاريخ","مراجعة مطلوبة",IF(H21="منتهي","عالية",IF(H21="حرج","عالية",IF(H21="قريب","متوسطة","منخفضة"))))</f>
-        <v>مراجعة مطلوبة</v>
+        <v>166</v>
+      </c>
+      <c r="E21" s="4">
+        <v>46599</v>
+      </c>
+      <c r="F21" s="5">
+        <f ca="1">E21-TODAY()</f>
+        <v>333</v>
+      </c>
+      <c r="G21" s="4">
+        <f t="shared" ref="G21" si="5">IF(E21="","",E21-30)</f>
+        <v>46569</v>
+      </c>
+      <c r="H21" s="12" t="str">
+        <f t="shared" ref="H21" ca="1" si="6">IF(E21="","بدون تاريخ",IF(F21&lt;0,"منتهي",IF(F21&lt;=30,"حرج",IF(F21&lt;=60,"قريب","ساري"))))</f>
+        <v>ساري</v>
+      </c>
+      <c r="I21" s="12" t="str">
+        <f t="shared" ref="I21" ca="1" si="7">IF(H21="بدون تاريخ","مراجعة مطلوبة",IF(H21="منتهي","عالية",IF(H21="حرج","عالية",IF(H21="قريب","متوسطة","منخفضة"))))</f>
+        <v>منخفضة</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>21</v>
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="7" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>23</v>
+        <v>162</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="P21" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q21" t="s">
         <v>27</v>
       </c>
       <c r="R21" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="E22" s="4"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H22" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v>بدون تاريخ</v>
-      </c>
-      <c r="I22" s="6" t="str">
-        <f t="shared" si="7"/>
-        <v>مراجعة مطلوبة</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K22" s="3"/>
-      <c r="L22" s="7" t="s">
         <v>159</v>
-      </c>
-      <c r="M22" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N22" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="P22" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>
